--- a/Tasks-Tracker-Import-Template.xlsx
+++ b/Tasks-Tracker-Import-Template.xlsx
@@ -449,13 +449,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,15 +467,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Week theme</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Work Item</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -488,15 +494,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Establish business</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>Research targeted customers</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -508,17 +519,18 @@
           <t>6/15/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>File LLC and apply EIN</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -532,15 +544,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>Networking</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>Research targeted customers</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
@@ -552,17 +569,18 @@
           <t>6/22/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Build a website</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
@@ -580,7 +598,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -694,8 +712,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -772,33 +790,47 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Status: Not started / In progress / Blocked / Closed ('done' also works). Progress % is set</t>
+          <t>Week theme: an optional label for the week (e.g. 'Establish business'). It only needs to appear</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>automatically from status; fine-tune it in the app afterward.</t>
+          <t>on one row of that week — leave it blank on the others.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Category: anything you like — new categories are created automatically.</t>
+          <t>Status: Not started / In progress / Blocked / Closed ('done' also works). Progress % is set</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Hours: decimal numbers, e.g. 1.5.</t>
+          <t>automatically from status; fine-tune it in the app afterward.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category: anything you like — new categories are created automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Hours: decimal numbers, e.g. 1.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>An item worked over several weeks = one plan row per week, same item name.</t>
         </is>

--- a/Tasks-Tracker-Import-Template.xlsx
+++ b/Tasks-Tracker-Import-Template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,16 +30,16 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000E2233"/>
-      <sz val="10"/>
     </font>
     <font>
       <color rgb="001B2B3A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,16 +74,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,14 +443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,11 +470,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
@@ -504,11 +492,6 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
           <t>Closed</t>
         </is>
       </c>
@@ -519,18 +502,13 @@
           <t>6/15/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>File LLC and apply EIN</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -554,11 +532,6 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
           <t>In progress</t>
         </is>
       </c>
@@ -569,18 +542,13 @@
           <t>6/22/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Build a website</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
@@ -597,14 +565,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,10 +594,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -650,10 +624,15 @@
           <t>Built list of 20 target companies</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Healthcare first</t>
         </is>
@@ -675,10 +654,15 @@
           <t>Filed LLC with the state</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -696,10 +680,15 @@
           <t>Outreach emails to first 5 targets</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -712,8 +701,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -746,9 +735,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -770,9 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-    </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -818,19 +801,26 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Category: anything you like — new categories are created automatically.</t>
+          <t>Category: enter it in Work Records — it only needs to appear once per item, and it carries</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Hours: decimal numbers, e.g. 1.5.</t>
+          <t>over automatically after that. New categories are created automatically.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Hours: decimal numbers, e.g. 1.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>An item worked over several weeks = one plan row per week, same item name.</t>
         </is>
